--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -1559,19 +1559,19 @@
         <v>80</v>
       </c>
       <c r="F2" t="n">
-        <v>99.99999999999999</v>
+        <v>100</v>
       </c>
       <c r="G2" t="n">
         <v>80</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>4.944420000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.045</v>
+        <v>0.04500000000000001</v>
       </c>
       <c r="R2" t="n">
         <v>12.32876712328767</v>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-3.552713678800501e-14</v>
       </c>
     </row>
     <row r="3">
@@ -1669,7 +1669,7 @@
         <v>153.0518</v>
       </c>
       <c r="P3" t="n">
-        <v>6.887331000000001</v>
+        <v>6.887331</v>
       </c>
       <c r="Q3" t="n">
         <v>0.04500000000000001</v>
@@ -1743,13 +1743,13 @@
         <v>30.82224430000005</v>
       </c>
       <c r="N4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="O4" t="n">
-        <v>203.1881999999999</v>
+        <v>203.1882</v>
       </c>
       <c r="P4" t="n">
-        <v>5.790863699999997</v>
+        <v>5.790863699999999</v>
       </c>
       <c r="Q4" t="n">
         <v>0.0285</v>
@@ -1761,7 +1761,7 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>26.28542482500007</v>
+        <v>26.28542482500006</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>2.842170943040401e-14</v>
       </c>
     </row>
     <row r="5">
@@ -1829,7 +1829,7 @@
         <v>261.7714</v>
       </c>
       <c r="P5" t="n">
-        <v>3.141256800000001</v>
+        <v>3.1412568</v>
       </c>
       <c r="Q5" t="n">
         <v>0.012</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-5.684341886080801e-14</v>
+        <v>-2.842170943040401e-14</v>
       </c>
     </row>
     <row r="6">
@@ -1903,10 +1903,10 @@
         <v>48.08252830000012</v>
       </c>
       <c r="N6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="O6" t="n">
-        <v>332.6215999999999</v>
+        <v>332.6216</v>
       </c>
       <c r="P6" t="n">
         <v>3.9914592</v>
@@ -1962,7 +1962,7 @@
         <v>390</v>
       </c>
       <c r="G7" t="n">
-        <v>250.0000000000001</v>
+        <v>250</v>
       </c>
       <c r="H7" t="n">
         <v>1</v>
@@ -1989,7 +1989,7 @@
         <v>394.7369</v>
       </c>
       <c r="P7" t="n">
-        <v>4.736842799999999</v>
+        <v>4.7368428</v>
       </c>
       <c r="Q7" t="n">
         <v>0.012</v>
@@ -8620,10 +8620,10 @@
         <v>161.7714</v>
       </c>
       <c r="M18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="N18" t="n">
-        <v>161.7714000000001</v>
+        <v>161.7714</v>
       </c>
       <c r="O18" t="n">
         <v>1</v>
@@ -10412,7 +10412,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
         <v>0.97</v>
@@ -21728,7 +21728,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>950.0000000000001</v>
+        <v>950</v>
       </c>
     </row>
     <row r="8">
@@ -21748,7 +21748,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1.4210854715202e-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -21828,7 +21828,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -21948,7 +21948,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>467.6336700000001</v>
+        <v>467.63367</v>
       </c>
     </row>
     <row r="19">

--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -423,13 +423,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>TerraPlan export</t>
+          <t>Выгрузка TerraPlan, версия</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>plan_id</t>
+          <t>план (plan_id)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>scenario_id</t>
+          <t>сценарий (scenario_id)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -465,96 +465,240 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>feasible</t>
+          <t>план исполним</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>да</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>unit:fuel</t>
+          <t>жёстких нарушений / отклонений от ориентиров / предупреждений</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>0 / 0 / 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>unit:money</t>
+          <t>единица: fuel</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>mln conventional units, constant 2035 prices</t>
+          <t>т</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>unit:capacity</t>
+          <t>единица: money</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t/year</t>
+          <t>млн у.е., постоянные цены 2035 г.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>unit:reservation_rate</t>
+          <t>единица: capacity</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>mln per (t/year)</t>
+          <t>т/год</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>unit:service_level</t>
+          <t>единица: reservation_rate</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>share 0..1</t>
+          <t>млн у.е. за (т/год)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>unit:time_step</t>
+          <t>единица: service_level</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>calendar month</t>
+          <t>доля 0..1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sheets</t>
+          <t>единица: time_step</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>календарный месяц</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>периоды</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2035-01 … 2040-12, шаг — календарный месяц; подготовительный период до 2035-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>листы</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>yearly_balance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>годовой баланс: спрос, выдача, дефицит, уровни сервиса, поступление, потери, запасы, 45-дневный резерв</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>inventory_trace</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>помесячный материальный баланс и стоимость хранения</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>source_schedule</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>по источникам и годам: резерв, заказ, план/факт поставки, цена, оплачиваемый объём (take-or-pay), платежи</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>financial_breakdown</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>по годам: закупка, резервирование, хранение, постоянный OPEX, CAPEX, итого, PV, накопленный CAPEX</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>constraint_checks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>нарушения: правило, строгость, год, месяц, источник, факт, лимит, превышение, сообщение</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>constraint_matrix</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>матрица проверок: каждое правило × год, включая выполненные</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>delivery_schedule</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>календарь поставок: месяц поставки, месяц размещения заказа, срок поставки, допустимость</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>kpi</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>итоговые показатели</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>investments</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>инвестиционные решения: даты опциона, реализации, ввода</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>assumptions</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>реестр допущений TEAM_ASSUMPTION: значение, единица, статус, диапазон, обоснование</t>
         </is>
       </c>
     </row>
@@ -774,7 +918,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>share per year (real)</t>
+          <t>доля в год (реальная ставка)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -789,7 +933,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Real discount rate for long-lived infrastructure with technology risk. Not given by the organizer. Used identically for all alternatives; sensitivity 0–12 % in experiments/run_sensitivity.py.
+          <t xml:space="preserve">Реальная ставка дисконтирования для долгоживущей инфраструктуры с технологическим риском. Организатором не задана. Применяется одинаково ко всем альтернативам; чувствительность 0–12 % в experiments/run_sensitivity.py.
 </t>
         </is>
       </c>
@@ -807,7 +951,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>год</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -822,7 +966,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year; PV factor = 1/(1+r)^(year-2035).</t>
+          <t>Годовые денежные потоки датируются началом каждого года; коэффициент приведения = 1/(1+r)^(год − 2035).</t>
         </is>
       </c>
     </row>
@@ -839,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>enum start|mid|end</t>
+          <t>перечисление start|mid|end</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -854,7 +998,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Annual cash flows dated at the start of each year (exponent year-2035); mid/end-year conventions available and applied identically to all alternatives.</t>
+          <t>Момент внутри года, к которому отнесён годовой поток — начало (показатель степени год − 2035), середина (+0,5) или конец (+1); одинаково для всех альтернатив.</t>
         </is>
       </c>
     </row>
@@ -871,7 +1015,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -886,7 +1030,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Earliest order date of the preparatory period (Earth-Core needs 12 months before 2035-01).</t>
+          <t>Самая ранняя дата заказа в подготовительном периоде (Earth-Core требует 12 месяцев до 2035-01).</t>
         </is>
       </c>
     </row>
@@ -903,7 +1047,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>enum min|max|mean</t>
+          <t>перечисление min|max|mean</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -918,7 +1062,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Conservative end of the organizer lead-time ranges (Earth-New 24 months, ISRU 2 months).</t>
+          <t>Консервативный край диапазонов сроков поставки организатора (Earth-New 24 месяца, ISRU 2 месяца).</t>
         </is>
       </c>
     </row>
@@ -935,7 +1079,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>weeks</t>
+          <t>недель</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -950,7 +1094,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>365/12/7. Week lead times converted with ceil(weeks/4.345) -&gt; Emergency 6 weeks = 2 months.</t>
+          <t>365/12/7. Сроки в неделях переводятся как ceil(недели/4,345) -&gt; Emergency 6 недель = 2 месяца.</t>
         </is>
       </c>
     </row>
@@ -967,7 +1111,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>дней</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -982,7 +1126,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>365/12; day-denominated lead times converted with ceil.</t>
+          <t>365/12; сроки в днях переводятся с округлением вверх.</t>
         </is>
       </c>
     </row>
@@ -999,7 +1143,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1014,7 +1158,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Case gives no ZBO build time; modernization active from the CAPEX month. Varied in sensitivity.</t>
+          <t>Кейс не задаёт срок модернизации ZBO; она считается действующей с месяца оплаты CAPEX. Варьируется в анализе чувствительности.</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1175,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>months</t>
+          <t>месяцев</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1046,7 +1190,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>The 18–24 month Earth-New lead time is read as decision-to-first-delivery; orders are placed during preparation.</t>
+          <t>Срок Earth-New 18–24 месяца трактуется как время от решения до первой поставки; заказы размещаются в период подготовки, после ввода дополнительный срок заказа 0 месяцев.</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1207,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1078,7 +1222,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunar-ISRU available from 2038 once CAPEX is financed before 2038.</t>
+          <t>Lunar-ISRU доступен с 2038 года при финансировании CAPEX до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1095,7 +1239,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>YYYY-MM</t>
+          <t>ГГГГ-ММ</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1110,7 +1254,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CAPEX 1250 must be financed before 2038.</t>
+          <t>CAPEX 1 250 млн должен быть профинансирован до 2038 года.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1271,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>map source_id -&gt; investment_id</t>
+          <t>отображение source_id -&gt; investment_id</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1142,7 +1286,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Earth-New capacity requires the exercised option; Lunar-ISRU requires the pilot CAPEX.</t>
+          <t>Мощность Earth-New требует реализованного опциона; Lunar-ISRU — CAPEX пилотного производства.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1303,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>map investment_id -&gt; storage_id</t>
+          <t>отображение investment_id -&gt; storage_id</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1174,7 +1318,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ZBO modernization switches the active storage mode (capacity 120 t, losses 1.2 %, OPEX 12/yr).</t>
+          <t>Модернизация ZBO переключает активный режим хранилища (ёмкость 120 т, потери 1,2 %, OPEX 12 млн/год).</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1335,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>share of annual total demand</t>
+          <t>доля годового общего спроса</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1206,7 +1350,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Emergency counts as the base channel in a year when its ordered volume exceeds 20 % of that year's demand.</t>
+          <t>Emergency считается базовым каналом в году, когда заказанный у него объём превышает 20 % спроса этого года.</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1367,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1238,7 +1382,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Average physical stock per month = (I_start + I_end)/2; holding = 0.72 x average x 1/12.</t>
+          <t>Средний физический запас за месяц = (I_start + I_end)/2; стоимость хранения = 0,72 × средний запас × 1/12.</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1399,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1270,7 +1414,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hard violation when end-of-month stock &gt; capacity; warning when stock after inflow (before withdrawals) &gt; capacity.</t>
+          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1431,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rule</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1302,7 +1446,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Contracted Emergency reserve counts only if stock covers demand during the 6-week lead time and reserved Emergency capacity &gt;= R_y.</t>
+          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
         </is>
       </c>
     </row>
@@ -1319,7 +1463,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1334,7 +1478,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>The preparatory-period purchase pays the source reservation rate on the purchased tonnage for one year; booked in 2035.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1495,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1366,7 +1510,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Holding cost charged from 2035-01; storage time in the preparatory period (&lt; 1 month) is not charged.</t>
+          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1527,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>enum</t>
+          <t>перечисление</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1398,7 +1542,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Organizer convention — uniform demand within the year, 365 days.</t>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
         </is>
       </c>
     </row>
@@ -11424,7 +11568,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11437,7 +11581,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11473,7 +11617,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11486,7 +11630,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11522,7 +11666,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11535,7 +11679,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11715,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11584,7 +11728,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11764,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11633,7 +11777,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -11669,7 +11813,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (else counts as base year)</t>
+          <t>&lt;= (иначе год считается базовым для Emergency)</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11682,7 +11826,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>max 2 consecutive base years</t>
+          <t>не более 2 базовых лет подряд</t>
         </is>
       </c>
     </row>
@@ -13695,7 +13839,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M143"/>
+  <dimension ref="A1:N143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13764,6 +13908,11 @@
           <t>lead_time_ok</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>lead_time_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -13819,6 +13968,11 @@
       <c r="M2" t="b">
         <v>1</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -13874,6 +14028,11 @@
       <c r="M3" t="b">
         <v>1</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -13929,6 +14088,11 @@
       <c r="M4" t="b">
         <v>1</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -13984,6 +14148,11 @@
       <c r="M5" t="b">
         <v>1</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14039,6 +14208,11 @@
       <c r="M6" t="b">
         <v>1</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14094,6 +14268,11 @@
       <c r="M7" t="b">
         <v>1</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14149,6 +14328,11 @@
       <c r="M8" t="b">
         <v>1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14204,6 +14388,11 @@
       <c r="M9" t="b">
         <v>1</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14259,6 +14448,11 @@
       <c r="M10" t="b">
         <v>1</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -14314,6 +14508,11 @@
       <c r="M11" t="b">
         <v>1</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -14369,6 +14568,11 @@
       <c r="M12" t="b">
         <v>1</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -14424,6 +14628,11 @@
       <c r="M13" t="b">
         <v>1</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -14479,6 +14688,11 @@
       <c r="M14" t="b">
         <v>1</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -14534,6 +14748,11 @@
       <c r="M15" t="b">
         <v>1</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -14589,6 +14808,11 @@
       <c r="M16" t="b">
         <v>1</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -14644,6 +14868,11 @@
       <c r="M17" t="b">
         <v>1</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -14699,6 +14928,11 @@
       <c r="M18" t="b">
         <v>1</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -14754,6 +14988,11 @@
       <c r="M19" t="b">
         <v>1</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -14809,6 +15048,11 @@
       <c r="M20" t="b">
         <v>1</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -14864,6 +15108,11 @@
       <c r="M21" t="b">
         <v>1</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -14919,6 +15168,11 @@
       <c r="M22" t="b">
         <v>1</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -14974,6 +15228,11 @@
       <c r="M23" t="b">
         <v>1</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -15029,6 +15288,11 @@
       <c r="M24" t="b">
         <v>1</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -15084,6 +15348,11 @@
       <c r="M25" t="b">
         <v>1</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -15139,6 +15408,11 @@
       <c r="M26" t="b">
         <v>1</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -15194,6 +15468,11 @@
       <c r="M27" t="b">
         <v>1</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -15249,6 +15528,11 @@
       <c r="M28" t="b">
         <v>1</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -15304,6 +15588,11 @@
       <c r="M29" t="b">
         <v>1</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -15359,6 +15648,11 @@
       <c r="M30" t="b">
         <v>1</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -15414,6 +15708,11 @@
       <c r="M31" t="b">
         <v>1</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -15469,6 +15768,11 @@
       <c r="M32" t="b">
         <v>1</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -15524,6 +15828,11 @@
       <c r="M33" t="b">
         <v>1</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -15579,6 +15888,11 @@
       <c r="M34" t="b">
         <v>1</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -15634,6 +15948,11 @@
       <c r="M35" t="b">
         <v>1</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -15689,6 +16008,11 @@
       <c r="M36" t="b">
         <v>1</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -15744,6 +16068,11 @@
       <c r="M37" t="b">
         <v>1</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -15799,6 +16128,11 @@
       <c r="M38" t="b">
         <v>1</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -15854,6 +16188,11 @@
       <c r="M39" t="b">
         <v>1</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -15909,6 +16248,11 @@
       <c r="M40" t="b">
         <v>1</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -15964,6 +16308,11 @@
       <c r="M41" t="b">
         <v>1</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -16019,6 +16368,11 @@
       <c r="M42" t="b">
         <v>1</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -16074,6 +16428,11 @@
       <c r="M43" t="b">
         <v>1</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -16129,6 +16488,11 @@
       <c r="M44" t="b">
         <v>1</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -16184,6 +16548,11 @@
       <c r="M45" t="b">
         <v>1</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -16239,6 +16608,11 @@
       <c r="M46" t="b">
         <v>1</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -16294,6 +16668,11 @@
       <c r="M47" t="b">
         <v>1</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -16349,6 +16728,11 @@
       <c r="M48" t="b">
         <v>1</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -16404,6 +16788,11 @@
       <c r="M49" t="b">
         <v>1</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -16459,6 +16848,11 @@
       <c r="M50" t="b">
         <v>1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -16514,6 +16908,11 @@
       <c r="M51" t="b">
         <v>1</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -16569,6 +16968,11 @@
       <c r="M52" t="b">
         <v>1</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -16624,6 +17028,11 @@
       <c r="M53" t="b">
         <v>1</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -16679,6 +17088,11 @@
       <c r="M54" t="b">
         <v>1</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -16734,6 +17148,11 @@
       <c r="M55" t="b">
         <v>1</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -16789,6 +17208,11 @@
       <c r="M56" t="b">
         <v>1</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -16844,6 +17268,11 @@
       <c r="M57" t="b">
         <v>1</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -16899,6 +17328,11 @@
       <c r="M58" t="b">
         <v>1</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -16954,6 +17388,11 @@
       <c r="M59" t="b">
         <v>1</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -17009,6 +17448,11 @@
       <c r="M60" t="b">
         <v>1</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -17064,6 +17508,11 @@
       <c r="M61" t="b">
         <v>1</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -17119,6 +17568,11 @@
       <c r="M62" t="b">
         <v>1</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -17174,6 +17628,11 @@
       <c r="M63" t="b">
         <v>1</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -17229,6 +17688,11 @@
       <c r="M64" t="b">
         <v>1</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -17284,6 +17748,11 @@
       <c r="M65" t="b">
         <v>1</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -17339,6 +17808,11 @@
       <c r="M66" t="b">
         <v>1</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17394,6 +17868,11 @@
       <c r="M67" t="b">
         <v>1</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17449,6 +17928,11 @@
       <c r="M68" t="b">
         <v>1</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17504,6 +17988,11 @@
       <c r="M69" t="b">
         <v>1</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17559,6 +18048,11 @@
       <c r="M70" t="b">
         <v>1</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -17614,6 +18108,11 @@
       <c r="M71" t="b">
         <v>1</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -17669,6 +18168,11 @@
       <c r="M72" t="b">
         <v>1</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -17724,6 +18228,11 @@
       <c r="M73" t="b">
         <v>1</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -17779,6 +18288,11 @@
       <c r="M74" t="b">
         <v>1</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -17834,6 +18348,11 @@
       <c r="M75" t="b">
         <v>1</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -17889,6 +18408,11 @@
       <c r="M76" t="b">
         <v>1</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -17944,6 +18468,11 @@
       <c r="M77" t="b">
         <v>1</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -17999,6 +18528,11 @@
       <c r="M78" t="b">
         <v>1</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -18054,6 +18588,11 @@
       <c r="M79" t="b">
         <v>1</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -18109,6 +18648,11 @@
       <c r="M80" t="b">
         <v>1</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -18164,6 +18708,11 @@
       <c r="M81" t="b">
         <v>1</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -18219,6 +18768,11 @@
       <c r="M82" t="b">
         <v>1</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -18274,6 +18828,11 @@
       <c r="M83" t="b">
         <v>1</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -18329,6 +18888,11 @@
       <c r="M84" t="b">
         <v>1</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -18384,6 +18948,11 @@
       <c r="M85" t="b">
         <v>1</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -18439,6 +19008,11 @@
       <c r="M86" t="b">
         <v>1</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -18494,6 +19068,11 @@
       <c r="M87" t="b">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -18549,6 +19128,11 @@
       <c r="M88" t="b">
         <v>1</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -18604,6 +19188,11 @@
       <c r="M89" t="b">
         <v>1</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -18659,6 +19248,11 @@
       <c r="M90" t="b">
         <v>1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -18714,6 +19308,11 @@
       <c r="M91" t="b">
         <v>1</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -18769,6 +19368,11 @@
       <c r="M92" t="b">
         <v>1</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -18824,6 +19428,11 @@
       <c r="M93" t="b">
         <v>1</v>
       </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -18879,6 +19488,11 @@
       <c r="M94" t="b">
         <v>1</v>
       </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -18934,6 +19548,11 @@
       <c r="M95" t="b">
         <v>1</v>
       </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -18989,6 +19608,11 @@
       <c r="M96" t="b">
         <v>1</v>
       </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -19044,6 +19668,11 @@
       <c r="M97" t="b">
         <v>1</v>
       </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -19099,6 +19728,11 @@
       <c r="M98" t="b">
         <v>1</v>
       </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -19154,6 +19788,11 @@
       <c r="M99" t="b">
         <v>1</v>
       </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -19209,6 +19848,11 @@
       <c r="M100" t="b">
         <v>1</v>
       </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -19264,6 +19908,11 @@
       <c r="M101" t="b">
         <v>1</v>
       </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -19319,6 +19968,11 @@
       <c r="M102" t="b">
         <v>1</v>
       </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -19374,6 +20028,11 @@
       <c r="M103" t="b">
         <v>1</v>
       </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -19429,6 +20088,11 @@
       <c r="M104" t="b">
         <v>1</v>
       </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -19484,6 +20148,11 @@
       <c r="M105" t="b">
         <v>1</v>
       </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -19539,6 +20208,11 @@
       <c r="M106" t="b">
         <v>1</v>
       </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -19594,6 +20268,11 @@
       <c r="M107" t="b">
         <v>1</v>
       </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -19649,6 +20328,11 @@
       <c r="M108" t="b">
         <v>1</v>
       </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -19704,6 +20388,11 @@
       <c r="M109" t="b">
         <v>1</v>
       </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -19759,6 +20448,11 @@
       <c r="M110" t="b">
         <v>1</v>
       </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -19814,6 +20508,11 @@
       <c r="M111" t="b">
         <v>1</v>
       </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -19869,6 +20568,11 @@
       <c r="M112" t="b">
         <v>1</v>
       </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -19924,6 +20628,11 @@
       <c r="M113" t="b">
         <v>1</v>
       </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -19979,6 +20688,11 @@
       <c r="M114" t="b">
         <v>1</v>
       </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -20034,6 +20748,11 @@
       <c r="M115" t="b">
         <v>1</v>
       </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -20089,6 +20808,11 @@
       <c r="M116" t="b">
         <v>1</v>
       </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -20144,6 +20868,11 @@
       <c r="M117" t="b">
         <v>1</v>
       </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -20199,6 +20928,11 @@
       <c r="M118" t="b">
         <v>1</v>
       </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -20254,6 +20988,11 @@
       <c r="M119" t="b">
         <v>1</v>
       </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -20309,6 +21048,11 @@
       <c r="M120" t="b">
         <v>1</v>
       </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -20364,6 +21108,11 @@
       <c r="M121" t="b">
         <v>1</v>
       </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -20419,6 +21168,11 @@
       <c r="M122" t="b">
         <v>1</v>
       </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -20474,6 +21228,11 @@
       <c r="M123" t="b">
         <v>1</v>
       </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -20529,6 +21288,11 @@
       <c r="M124" t="b">
         <v>1</v>
       </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -20584,6 +21348,11 @@
       <c r="M125" t="b">
         <v>1</v>
       </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -20639,6 +21408,11 @@
       <c r="M126" t="b">
         <v>1</v>
       </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -20694,6 +21468,11 @@
       <c r="M127" t="b">
         <v>1</v>
       </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -20749,6 +21528,11 @@
       <c r="M128" t="b">
         <v>1</v>
       </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -20804,6 +21588,11 @@
       <c r="M129" t="b">
         <v>1</v>
       </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -20859,6 +21648,11 @@
       <c r="M130" t="b">
         <v>1</v>
       </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -20914,6 +21708,11 @@
       <c r="M131" t="b">
         <v>1</v>
       </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -20969,6 +21768,11 @@
       <c r="M132" t="b">
         <v>1</v>
       </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -21024,6 +21828,11 @@
       <c r="M133" t="b">
         <v>1</v>
       </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -21079,6 +21888,11 @@
       <c r="M134" t="b">
         <v>1</v>
       </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -21134,6 +21948,11 @@
       <c r="M135" t="b">
         <v>1</v>
       </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -21189,6 +22008,11 @@
       <c r="M136" t="b">
         <v>1</v>
       </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -21244,6 +22068,11 @@
       <c r="M137" t="b">
         <v>1</v>
       </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -21299,6 +22128,11 @@
       <c r="M138" t="b">
         <v>1</v>
       </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -21354,6 +22188,11 @@
       <c r="M139" t="b">
         <v>1</v>
       </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -21409,6 +22248,11 @@
       <c r="M140" t="b">
         <v>1</v>
       </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -21464,6 +22308,11 @@
       <c r="M141" t="b">
         <v>1</v>
       </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>срок поставки 12 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -21519,6 +22368,11 @@
       <c r="M142" t="b">
         <v>1</v>
       </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>срок поставки 4 мес.; заказы с 2034-01</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -21573,6 +22427,11 @@
       </c>
       <c r="M143" t="b">
         <v>1</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>ввод 2038-01; срок поставки после ввода 2 мес.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1543,6 +1543,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -11557,18 +11590,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -11581,7 +11614,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11606,18 +11639,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -11630,7 +11663,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11655,18 +11688,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -11679,7 +11712,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11704,18 +11737,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -11728,7 +11761,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11753,18 +11786,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -11777,7 +11810,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11802,18 +11835,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -11826,7 +11859,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -11851,7 +11884,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -11875,7 +11908,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12086,7 +12119,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12110,7 +12143,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12321,11 +12354,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>30.82224430000005</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G45" t="n">
         <v>70</v>
@@ -12345,7 +12378,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12654,7 +12687,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -12678,7 +12711,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12987,7 +13020,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -13011,7 +13044,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13418,7 +13451,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -13442,7 +13475,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -870,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1575,6 +1575,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -7538,7 +7538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7647,6 +7647,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7722,6 +7727,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7797,6 +7805,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7872,6 +7883,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7947,6 +7961,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8022,6 +8039,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8097,6 +8117,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8172,6 +8195,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8247,6 +8273,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8322,6 +8351,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8397,6 +8429,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8472,6 +8507,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8547,6 +8585,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8622,6 +8663,9 @@
       <c r="U14" t="n">
         <v>1.97835</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8697,6 +8741,9 @@
       <c r="U15" t="n">
         <v>0</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8772,6 +8819,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8847,6 +8897,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8922,6 +8975,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8997,6 +9053,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9072,6 +9131,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9147,6 +9209,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9222,6 +9287,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9297,6 +9365,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9372,6 +9443,9 @@
       <c r="U24" t="n">
         <v>3.3933</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9447,6 +9521,9 @@
       <c r="U25" t="n">
         <v>0</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9522,6 +9599,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9597,6 +9677,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9672,6 +9755,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9747,6 +9833,9 @@
       <c r="U29" t="n">
         <v>12.71055</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9822,6 +9911,9 @@
       <c r="U30" t="n">
         <v>0</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9897,6 +9989,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -9970,6 +10065,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9984,7 +10082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10048,6 +10146,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10090,6 +10193,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10132,6 +10238,9 @@
       <c r="L3" t="n">
         <v>1250</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10174,6 +10283,9 @@
       <c r="L4" t="n">
         <v>1430</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10216,6 +10328,9 @@
       <c r="L5" t="n">
         <v>1430</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10258,6 +10373,9 @@
       <c r="L6" t="n">
         <v>1430</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10299,6 +10417,9 @@
       </c>
       <c r="L7" t="n">
         <v>1430</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -22577,7 +22698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23015,11 +23136,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23035,11 +23156,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>48.08258550000025</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23055,11 +23176,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>48.08258550000025</v>
       </c>
     </row>
     <row r="25">
@@ -23075,7 +23196,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -23095,7 +23216,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -23115,11 +23236,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>1</v>
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -23135,11 +23256,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -23155,10 +23276,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>75</v>
       </c>
     </row>

--- a/results/alternatives/P3_isru_zbo_BASE/results.xlsx
+++ b/results/alternatives/P3_isru_zbo_BASE/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -870,7 +872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1394,7 +1396,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1414,24 +1416,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1441,29 +1443,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1473,29 +1475,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1505,176 +1507,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2305,7 +2450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2556,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2483,6 +2638,12 @@
         <v>0.7520604900000002</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2554,6 +2715,12 @@
         <v>0.7767183900000002</v>
       </c>
       <c r="U3" t="n">
+        <v>21.48412233333334</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2625,6 +2792,12 @@
         <v>0.8013762900000003</v>
       </c>
       <c r="U4" t="n">
+        <v>21.89508733333334</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2696,6 +2869,12 @@
         <v>0.8260341900000004</v>
       </c>
       <c r="U5" t="n">
+        <v>22.30605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2767,6 +2946,12 @@
         <v>0.8506920900000003</v>
       </c>
       <c r="U6" t="n">
+        <v>22.71701733333334</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2838,6 +3023,12 @@
         <v>0.8753499900000005</v>
       </c>
       <c r="U7" t="n">
+        <v>23.12798233333334</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2909,6 +3100,12 @@
         <v>0.9000078900000005</v>
       </c>
       <c r="U8" t="n">
+        <v>23.53894733333334</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2980,6 +3177,12 @@
         <v>0.9246657900000006</v>
       </c>
       <c r="U9" t="n">
+        <v>23.94991233333334</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3051,6 +3254,12 @@
         <v>0.9493236900000007</v>
       </c>
       <c r="U10" t="n">
+        <v>24.36087733333335</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3122,6 +3331,12 @@
         <v>0.973981590000001</v>
       </c>
       <c r="U11" t="n">
+        <v>24.77184233333335</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3193,6 +3408,12 @@
         <v>0.9986394900000012</v>
       </c>
       <c r="U12" t="n">
+        <v>25.18280733333335</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3264,6 +3485,12 @@
         <v>1.023297390000001</v>
       </c>
       <c r="U13" t="n">
+        <v>25.59377233333336</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3335,6 +3562,12 @@
         <v>1.051037512500002</v>
       </c>
       <c r="U14" t="n">
+        <v>29.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3406,6 +3639,12 @@
         <v>1.081859857500002</v>
       </c>
       <c r="U15" t="n">
+        <v>29.95451716666669</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3477,6 +3716,12 @@
         <v>1.112682202500001</v>
       </c>
       <c r="U16" t="n">
+        <v>30.46822291666669</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3548,6 +3793,12 @@
         <v>1.143504547500002</v>
       </c>
       <c r="U17" t="n">
+        <v>30.98192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3619,6 +3870,12 @@
         <v>1.174326892500001</v>
       </c>
       <c r="U18" t="n">
+        <v>31.49563441666669</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3690,6 +3947,12 @@
         <v>1.205149237500002</v>
       </c>
       <c r="U19" t="n">
+        <v>32.00934016666669</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3761,6 +4024,12 @@
         <v>1.235971582500002</v>
       </c>
       <c r="U20" t="n">
+        <v>32.5230459166667</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3832,6 +4101,12 @@
         <v>1.266793927500003</v>
       </c>
       <c r="U21" t="n">
+        <v>33.0367516666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3903,6 +4178,12 @@
         <v>1.297616272500003</v>
       </c>
       <c r="U22" t="n">
+        <v>33.55045741666671</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3974,6 +4255,12 @@
         <v>1.328438617500003</v>
       </c>
       <c r="U23" t="n">
+        <v>34.06416316666672</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4045,6 +4332,12 @@
         <v>1.359260962500004</v>
       </c>
       <c r="U24" t="n">
+        <v>34.57786891666672</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4116,6 +4409,12 @@
         <v>1.390083307500004</v>
       </c>
       <c r="U25" t="n">
+        <v>35.09157466666673</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4187,6 +4486,12 @@
         <v>1.415606307500004</v>
       </c>
       <c r="U26" t="n">
+        <v>39.59530225000007</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4258,6 +4563,12 @@
         <v>1.435829962500004</v>
       </c>
       <c r="U27" t="n">
+        <v>39.93236316666674</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4329,6 +4640,12 @@
         <v>1.456053617500004</v>
       </c>
       <c r="U28" t="n">
+        <v>40.2694240833334</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4400,6 +4717,12 @@
         <v>1.476277272500004</v>
       </c>
       <c r="U29" t="n">
+        <v>40.60648500000007</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4471,6 +4794,12 @@
         <v>1.496500927500004</v>
       </c>
       <c r="U30" t="n">
+        <v>40.94354591666674</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4542,6 +4871,12 @@
         <v>1.516724582500004</v>
       </c>
       <c r="U31" t="n">
+        <v>41.2806068333334</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4613,6 +4948,12 @@
         <v>1.553711264000004</v>
       </c>
       <c r="U32" t="n">
+        <v>42.17643530000007</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4684,6 +5025,12 @@
         <v>1.607460972000004</v>
       </c>
       <c r="U33" t="n">
+        <v>43.07226376666673</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4755,6 +5102,12 @@
         <v>1.661210680000003</v>
       </c>
       <c r="U34" t="n">
+        <v>43.96809223333339</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4826,6 +5179,12 @@
         <v>1.714960388000003</v>
       </c>
       <c r="U35" t="n">
+        <v>44.86392070000006</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4897,6 +5256,12 @@
         <v>1.768710096000003</v>
       </c>
       <c r="U36" t="n">
+        <v>45.75974916666672</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4968,6 +5333,12 @@
         <v>1.822459804000003</v>
       </c>
       <c r="U37" t="n">
+        <v>46.65557763333339</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5039,6 +5410,12 @@
         <v>1.623910016000003</v>
       </c>
       <c r="U38" t="n">
+        <v>44.14142290000005</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5110,6 +5487,12 @@
         <v>1.173060732000003</v>
       </c>
       <c r="U39" t="n">
+        <v>36.62726816666672</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5181,6 +5564,12 @@
         <v>1.018611448000003</v>
       </c>
       <c r="U40" t="n">
+        <v>38.99311343333338</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5252,6 +5641,12 @@
         <v>1.160562164000004</v>
       </c>
       <c r="U41" t="n">
+        <v>41.35895870000006</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5323,6 +5718,12 @@
         <v>1.302512880000004</v>
       </c>
       <c r="U42" t="n">
+        <v>43.72480396666673</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5394,6 +5795,12 @@
         <v>1.444463596000004</v>
       </c>
       <c r="U43" t="n">
+        <v>46.09064923333339</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5465,6 +5872,12 @@
         <v>1.586414312000004</v>
       </c>
       <c r="U44" t="n">
+        <v>48.45649450000006</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5536,6 +5949,12 @@
         <v>1.728365028000004</v>
       </c>
       <c r="U45" t="n">
+        <v>50.82233976666673</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5607,6 +6026,12 @@
         <v>1.870315744000004</v>
       </c>
       <c r="U46" t="n">
+        <v>53.1881850333334</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5678,6 +6103,12 @@
         <v>2.012266460000004</v>
       </c>
       <c r="U47" t="n">
+        <v>55.55403030000006</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5749,6 +6180,12 @@
         <v>2.154217176000004</v>
       </c>
       <c r="U48" t="n">
+        <v>57.91987556666673</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5820,6 +6257,12 @@
         <v>2.296167892000004</v>
       </c>
       <c r="U49" t="n">
+        <v>60.2857208333334</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5891,6 +6334,12 @@
         <v>2.388718602000004</v>
       </c>
       <c r="U50" t="n">
+        <v>66.83823256666673</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5962,6 +6411,12 @@
         <v>2.431869306000004</v>
       </c>
       <c r="U51" t="n">
+        <v>67.55741096666674</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6033,6 +6488,12 @@
         <v>2.475020010000005</v>
       </c>
       <c r="U52" t="n">
+        <v>68.27658936666674</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6104,6 +6565,12 @@
         <v>2.518170714000005</v>
       </c>
       <c r="U53" t="n">
+        <v>68.99576776666675</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6175,6 +6642,12 @@
         <v>2.561321418000005</v>
       </c>
       <c r="U54" t="n">
+        <v>69.71494616666675</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6246,6 +6719,12 @@
         <v>2.604472122000006</v>
       </c>
       <c r="U55" t="n">
+        <v>70.43412456666675</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6317,6 +6796,12 @@
         <v>2.647622826000006</v>
       </c>
       <c r="U56" t="n">
+        <v>71.15330296666676</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6388,6 +6873,12 @@
         <v>2.690773530000006</v>
       </c>
       <c r="U57" t="n">
+        <v>71.87248136666676</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6459,6 +6950,12 @@
         <v>2.733924234000007</v>
       </c>
       <c r="U58" t="n">
+        <v>72.59165976666677</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6530,6 +7027,12 @@
         <v>2.777074938000007</v>
       </c>
       <c r="U59" t="n">
+        <v>73.31083816666677</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6601,6 +7104,12 @@
         <v>2.820225642000007</v>
       </c>
       <c r="U60" t="n">
+        <v>74.03001656666677</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6672,6 +7181,12 @@
         <v>2.863376346000007</v>
       </c>
       <c r="U61" t="n">
+        <v>74.74919496666678</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6743,6 +7258,12 @@
         <v>2.884951841000007</v>
       </c>
       <c r="U62" t="n">
+        <v>80.5825330666668</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6814,6 +7335,12 @@
         <v>2.884952127000008</v>
       </c>
       <c r="U63" t="n">
+        <v>80.58253783333348</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6885,6 +7412,12 @@
         <v>2.884952413000009</v>
       </c>
       <c r="U64" t="n">
+        <v>80.58254260000015</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6956,6 +7489,12 @@
         <v>2.88495269900001</v>
       </c>
       <c r="U65" t="n">
+        <v>80.58254736666683</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7027,6 +7566,12 @@
         <v>2.88495298500001</v>
       </c>
       <c r="U66" t="n">
+        <v>80.58255213333351</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7098,6 +7643,12 @@
         <v>2.884953271000011</v>
       </c>
       <c r="U67" t="n">
+        <v>80.58255690000018</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7169,6 +7720,12 @@
         <v>2.884953557000011</v>
       </c>
       <c r="U68" t="n">
+        <v>80.58256166666686</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7240,6 +7797,12 @@
         <v>2.884953843000012</v>
       </c>
       <c r="U69" t="n">
+        <v>80.58256643333354</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7311,6 +7874,12 @@
         <v>2.884954129000012</v>
       </c>
       <c r="U70" t="n">
+        <v>80.58257120000022</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7382,6 +7951,12 @@
         <v>2.884954415000013</v>
       </c>
       <c r="U71" t="n">
+        <v>80.58257596666689</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7453,6 +8028,12 @@
         <v>2.884954701000014</v>
       </c>
       <c r="U72" t="n">
+        <v>80.58258073333357</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7524,6 +8105,12 @@
         <v>2.884954987000015</v>
       </c>
       <c r="U73" t="n">
+        <v>80.58258550000025</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10173,7 +10760,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>10.65214728000001</v>
+        <v>11.02201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10182,13 +10769,13 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>858.16123728</v>
+        <v>858.5311030500001</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -10454,7 +11041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12145,7 +12732,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12153,14 +12740,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>25.59377233333336</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12177,7 +12764,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12194,7 +12781,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12202,14 +12789,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12243,7 +12830,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12251,18 +12838,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -12272,7 +12860,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12287,7 +12879,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12295,7 +12887,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -12331,27 +12923,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>23.42490800000007</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -12361,11 +12952,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-12, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12380,7 +12967,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12388,14 +12975,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>23.42490800000007</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12412,7 +12999,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12429,7 +13016,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12437,14 +13024,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>35.09157466666673</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -12461,7 +13048,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-12, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12478,7 +13065,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12486,170 +13073,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>25.44727350000007</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-06, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12664,7 +13251,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12672,14 +13259,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>25.44727350000007</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -12696,7 +13283,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-06, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12713,7 +13300,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12721,14 +13308,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_B_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>13.189</v>
+        <v>41.2806068333334</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -12745,7 +13332,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2037-06, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12762,7 +13349,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12770,14 +13357,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -12794,7 +13381,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -12811,7 +13398,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12819,219 +13406,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G51" t="n">
+        <v>110</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>39.45238750000007</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G54" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13046,7 +13633,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13054,11 +13641,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>120</v>
+        <v>39.45238750000007</v>
       </c>
       <c r="G55" t="n">
         <v>120</v>
@@ -13078,7 +13665,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13095,7 +13682,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13103,14 +13690,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>60.2857208333334</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -13127,7 +13714,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13144,7 +13731,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13152,268 +13739,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G58" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>120</v>
+      </c>
+      <c r="G59" t="n">
+        <v>120</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>48.08252830000012</v>
-      </c>
-      <c r="G59" t="n">
-        <v>120</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>22.622</v>
-      </c>
-      <c r="G62" t="n">
-        <v>110</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13428,7 +14015,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -13436,14 +14023,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_B_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>22.6216</v>
+        <v>48.08252830000012</v>
       </c>
       <c r="G63" t="n">
-        <v>22.622</v>
+        <v>120</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -13460,7 +14047,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-Flex</t>
+          <t>2039-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13477,7 +14064,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -13485,11 +14072,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>120</v>
+        <v>74.74919496666678</v>
       </c>
       <c r="G64" t="n">
         <v>120</v>
@@ -13509,7 +14096,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13526,7 +14113,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -13534,14 +14121,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -13558,7 +14145,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13575,7 +14162,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13583,317 +14170,317 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="G67" t="n">
+        <v>110</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>22.6216</v>
+      </c>
+      <c r="G68" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>120</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <f>=</f>
         <v/>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D72" t="n">
         <v>2039</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72">
         <f>=</f>
         <v/>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>48.08258550000025</v>
-      </c>
-      <c r="G68" t="n">
-        <v>120</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2040-12, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>190</v>
-      </c>
-      <c r="G69" t="n">
-        <v>190</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>190</v>
-      </c>
-      <c r="G70" t="n">
-        <v>190</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_B_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="G71" t="n">
-        <v>110</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_B_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>84.73690000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-Flex</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -13908,7 +14495,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -13916,11 +14503,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>120</v>
+        <v>48.08258550000025</v>
       </c>
       <c r="G73" t="n">
         <v>120</v>
@@ -13940,7 +14527,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13957,7 +14544,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -13965,11 +14552,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>120</v>
+        <v>80.58258550000025</v>
       </c>
       <c r="G74" t="n">
         <v>120</v>
@@ -13989,7 +14576,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-12, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14006,7 +14593,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -14014,72 +14601,366 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>190</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>190</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>reserved_B_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>110</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_B_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>84.73690000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-Flex</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>120</v>
+      </c>
+      <c r="G79" t="n">
+        <v>120</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>120</v>
+      </c>
+      <c r="G80" t="n">
+        <v>120</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <f>=</f>
         <v/>
       </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P3_isru_zbo</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D82" t="n">
         <v>2040</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82">
         <f>=</f>
         <v/>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -22698,7 +23579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22740,7 +23621,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10654.258816178</v>
+        <v>10654.628681948</v>
       </c>
     </row>
     <row r="3">
@@ -22760,7 +23641,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8638.856936167749</v>
+        <v>8639.226801937748</v>
       </c>
     </row>
     <row r="4">
@@ -22900,7 +23781,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.664934400128057</v>
+        <v>7.665200490610071</v>
       </c>
     </row>
     <row r="11">
@@ -22920,7 +23801,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.21500499004874</v>
+        <v>6.215271080530754</v>
       </c>
     </row>
     <row r="12">
@@ -23080,7 +23961,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>129.7272561780003</v>
+        <v>130.0971219480003</v>
       </c>
     </row>
     <row r="20">
@@ -23196,11 +24077,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23216,11 +24097,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23236,7 +24117,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -23256,11 +24137,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>1</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23276,11 +24157,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23296,11 +24177,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P3_isru_zbo</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>75</v>
+      <c r="D32" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
